--- a/anssi-guide_Lhernout_Cubizolles_Robain_Karbosky.xlsx
+++ b/anssi-guide_Lhernout_Cubizolles_Robain_Karbosky.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29917"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F1C9792E-EB46-4176-9084-28A04F454CD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{22F95796-4D93-4D3A-BCAC-59E6ED6524B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16460" tabRatio="813" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="447" uniqueCount="204">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="458" uniqueCount="215">
   <si>
     <t>* Licence ouverte / Open Licence v2.0.
 Page web, Mission Etalab, avril 2017.
@@ -108,7 +108,13 @@
     <t>Non</t>
   </si>
   <si>
-    <t>Désactivation des services inutiles (CDP, PAD, serveur HTTP non sécurisé) sur les interfaces publiques.</t>
+    <t>Exclue</t>
+  </si>
+  <si>
+    <t>Problème !</t>
+  </si>
+  <si>
+    <t>Si un mot de passe est "hardcodé", il faut isoler l'équipement dans un VLAN mort ou restreindre son accès via une ACL.</t>
   </si>
   <si>
     <t>R2</t>
@@ -135,18 +141,27 @@
     <t>Définir et utiliser des configurations de référence</t>
   </si>
   <si>
+    <t>acune reference utiliser lors de la configuration des equipement réseaux</t>
+  </si>
+  <si>
     <t>R4</t>
   </si>
   <si>
     <t>Établir un inventaire technique des éléments et des accès au SIE</t>
   </si>
   <si>
+    <t>L'inventaire est implicite via le schéma Packet Tracer ; pas de base de données d'inventaire séparée.</t>
+  </si>
+  <si>
     <t>R5</t>
   </si>
   <si>
     <t>Utiliser uniquement des équipements maîtrisés</t>
   </si>
   <si>
+    <t>Dans le cadre académique, les images IOS (systèmes des routeurs) sont imposées par le logiciel de simulation.</t>
+  </si>
+  <si>
     <t>R6</t>
   </si>
   <si>
@@ -258,6 +273,9 @@
     <t>Accès public : authentifier les utilisateurs</t>
   </si>
   <si>
+    <t>Packet Tracer ne permet pas d'intégrer nativement des serveurs d'authentification multifacteur (type Radius/OTP).</t>
+  </si>
+  <si>
     <t>R17+</t>
   </si>
   <si>
@@ -282,7 +300,7 @@
     <t>Accès nomade : chiffrer intégralement le disque du poste</t>
   </si>
   <si>
-    <t>Application d'une règle "Deny Any Any" en fin d'ACL pour respecter le principe du moindre privilège.</t>
+    <t>Limitation logicielle : les terminaux (End Devices) de Packet Tracer ne simulent pas le chiffrement de partition.</t>
   </si>
   <si>
     <t>R21</t>
@@ -354,7 +372,7 @@
     <t>Utiliser des comptes d’administration dédiés</t>
   </si>
   <si>
-    <t>Séparation des comptes utilisateurs simples et des comptes "admin" avec privilèges élevés (Level 15 sur Cisco).</t>
+    <t xml:space="preserve">compte admin non mis en place du a packet tracer </t>
   </si>
   <si>
     <t>R29-</t>
@@ -381,7 +399,7 @@
     <t>Protéger l’accès aux annuaires des comptes d’administration</t>
   </si>
   <si>
-    <t>Utilisation de SSH pour l'administration des routeurs et HTTPS pour l'interface de gestion.</t>
+    <t>Utilisation de HTTPS pour l'interface de gestion.</t>
   </si>
   <si>
     <t>R33</t>
@@ -417,7 +435,7 @@
     <t>Utiliser un poste d’administration dédié</t>
   </si>
   <si>
-    <t>Utilisation de mots de passe complexes et chiffrement des mots de passe dans la config (service password-encryption).</t>
+    <t>config fais sur packet tracer pas de post dedié</t>
   </si>
   <si>
     <t>R37-</t>
@@ -477,7 +495,7 @@
     <t>Utiliser des protocoles sécurisés pour l’administration</t>
   </si>
   <si>
-    <t>Activation de SSH v2. Désactivation de Telnet (flux en clair).</t>
+    <t xml:space="preserve">SSH non activer </t>
   </si>
   <si>
     <t>R43</t>
@@ -534,7 +552,7 @@
     <t>Dédier un mot de passe à chaque compte privilégié</t>
   </si>
   <si>
-    <t>Utilisation de service password-encryption et enable secret (hachage MD5/SHA) au lieu de enable password.</t>
+    <t xml:space="preserve">pas de compte privilegier donc pas de mdp </t>
   </si>
   <si>
     <t>R50</t>
@@ -543,6 +561,9 @@
     <t>Stocker les mots de passe dans un coffre-fort de mots de passe</t>
   </si>
   <si>
+    <t>Gestion manuelle des secrets pour la démonstration de la SAÉ. Utilisation de enable secret pour la protection locale.</t>
+  </si>
+  <si>
     <t>R51</t>
   </si>
   <si>
@@ -585,6 +606,9 @@
     <t>Définir une traçabilité des comptes privilégiés</t>
   </si>
   <si>
+    <t>L'envoi des logs vers un serveur Syslog externe n'a pas été implémenté pour simplifier la démonstration du tunnel.</t>
+  </si>
+  <si>
     <t>R57</t>
   </si>
   <si>
@@ -597,30 +621,45 @@
     <t>Documenter une politique de MCS</t>
   </si>
   <si>
+    <t>Mesure purement administrative et documentaire, hors du périmètre technique de la SAÉ.</t>
+  </si>
+  <si>
     <t>R59</t>
   </si>
   <si>
     <t>Mettre en place une veille de sécurité</t>
   </si>
   <si>
+    <t>Action humaine continue non simulable dans une maquette réseau ponctuelle.</t>
+  </si>
+  <si>
     <t>R60</t>
   </si>
   <si>
     <t>Obtenir des mises à jour de sécurité officielles</t>
   </si>
   <si>
+    <t>Environnement de lab statique. Les versions d'IOS (système Cisco) sont figées par le simulateur.</t>
+  </si>
+  <si>
     <t>R61</t>
   </si>
   <si>
     <t>Appliquer les mises à jour de sécurité</t>
   </si>
   <si>
+    <t>Environnement figé (maquette de démonstration). Les correctifs de sécurité ne sont pas applicables sur Packet Tracer.</t>
+  </si>
+  <si>
     <t>R62</t>
   </si>
   <si>
     <t>Utiliser des logiciels et des matériels supportés</t>
   </si>
   <si>
+    <t>Dépendance directe vis-à-vis des versions logicielles disponibles dans la bibliothèque Cisco Packet Tracer.</t>
+  </si>
+  <si>
     <t>R62-</t>
   </si>
   <si>
@@ -640,9 +679,6 @@
   </si>
   <si>
     <t>Pas commencé</t>
-  </si>
-  <si>
-    <t>Problème !</t>
   </si>
   <si>
     <r>
@@ -689,9 +725,6 @@
   </si>
   <si>
     <t>Ces valeurs, tout comme l'ensemble du présent document, sont personnalisables autant que de besoin.</t>
-  </si>
-  <si>
-    <t>Exclue</t>
   </si>
 </sst>
 </file>
@@ -1296,48 +1329,48 @@
     </xf>
   </cellXfs>
   <cellStyles count="42">
-    <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
-    <cellStyle name="20% - Accent2" xfId="23" builtinId="34" customBuiltin="1"/>
-    <cellStyle name="20% - Accent3" xfId="27" builtinId="38" customBuiltin="1"/>
-    <cellStyle name="20% - Accent4" xfId="31" builtinId="42" customBuiltin="1"/>
-    <cellStyle name="20% - Accent5" xfId="35" builtinId="46" customBuiltin="1"/>
-    <cellStyle name="20% - Accent6" xfId="39" builtinId="50" customBuiltin="1"/>
-    <cellStyle name="40% - Accent1" xfId="20" builtinId="31" customBuiltin="1"/>
-    <cellStyle name="40% - Accent2" xfId="24" builtinId="35" customBuiltin="1"/>
-    <cellStyle name="40% - Accent3" xfId="28" builtinId="39" customBuiltin="1"/>
-    <cellStyle name="40% - Accent4" xfId="32" builtinId="43" customBuiltin="1"/>
-    <cellStyle name="40% - Accent5" xfId="36" builtinId="47" customBuiltin="1"/>
-    <cellStyle name="40% - Accent6" xfId="40" builtinId="51" customBuiltin="1"/>
-    <cellStyle name="60% - Accent1" xfId="21" builtinId="32" customBuiltin="1"/>
-    <cellStyle name="60% - Accent2" xfId="25" builtinId="36" customBuiltin="1"/>
-    <cellStyle name="60% - Accent3" xfId="29" builtinId="40" customBuiltin="1"/>
-    <cellStyle name="60% - Accent4" xfId="33" builtinId="44" customBuiltin="1"/>
-    <cellStyle name="60% - Accent5" xfId="37" builtinId="48" customBuiltin="1"/>
-    <cellStyle name="60% - Accent6" xfId="41" builtinId="52" customBuiltin="1"/>
+    <cellStyle name="20 % - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
+    <cellStyle name="20 % - Accent2" xfId="23" builtinId="34" customBuiltin="1"/>
+    <cellStyle name="20 % - Accent3" xfId="27" builtinId="38" customBuiltin="1"/>
+    <cellStyle name="20 % - Accent4" xfId="31" builtinId="42" customBuiltin="1"/>
+    <cellStyle name="20 % - Accent5" xfId="35" builtinId="46" customBuiltin="1"/>
+    <cellStyle name="20 % - Accent6" xfId="39" builtinId="50" customBuiltin="1"/>
+    <cellStyle name="40 % - Accent1" xfId="20" builtinId="31" customBuiltin="1"/>
+    <cellStyle name="40 % - Accent2" xfId="24" builtinId="35" customBuiltin="1"/>
+    <cellStyle name="40 % - Accent3" xfId="28" builtinId="39" customBuiltin="1"/>
+    <cellStyle name="40 % - Accent4" xfId="32" builtinId="43" customBuiltin="1"/>
+    <cellStyle name="40 % - Accent5" xfId="36" builtinId="47" customBuiltin="1"/>
+    <cellStyle name="40 % - Accent6" xfId="40" builtinId="51" customBuiltin="1"/>
+    <cellStyle name="60 % - Accent1" xfId="21" builtinId="32" customBuiltin="1"/>
+    <cellStyle name="60 % - Accent2" xfId="25" builtinId="36" customBuiltin="1"/>
+    <cellStyle name="60 % - Accent3" xfId="29" builtinId="40" customBuiltin="1"/>
+    <cellStyle name="60 % - Accent4" xfId="33" builtinId="44" customBuiltin="1"/>
+    <cellStyle name="60 % - Accent5" xfId="37" builtinId="48" customBuiltin="1"/>
+    <cellStyle name="60 % - Accent6" xfId="41" builtinId="52" customBuiltin="1"/>
     <cellStyle name="Accent1" xfId="18" builtinId="29" customBuiltin="1"/>
     <cellStyle name="Accent2" xfId="22" builtinId="33" customBuiltin="1"/>
     <cellStyle name="Accent3" xfId="26" builtinId="37" customBuiltin="1"/>
     <cellStyle name="Accent4" xfId="30" builtinId="41" customBuiltin="1"/>
     <cellStyle name="Accent5" xfId="34" builtinId="45" customBuiltin="1"/>
     <cellStyle name="Accent6" xfId="38" builtinId="49" customBuiltin="1"/>
-    <cellStyle name="Bad" xfId="7" builtinId="27" customBuiltin="1"/>
-    <cellStyle name="Calculation" xfId="11" builtinId="22" customBuiltin="1"/>
-    <cellStyle name="Check Cell" xfId="13" builtinId="23" customBuiltin="1"/>
-    <cellStyle name="Explanatory Text" xfId="16" builtinId="53" customBuiltin="1"/>
-    <cellStyle name="Good" xfId="6" builtinId="26" customBuiltin="1"/>
-    <cellStyle name="Heading 1" xfId="2" builtinId="16" customBuiltin="1"/>
-    <cellStyle name="Heading 2" xfId="3" builtinId="17" customBuiltin="1"/>
-    <cellStyle name="Heading 3" xfId="4" builtinId="18" customBuiltin="1"/>
-    <cellStyle name="Heading 4" xfId="5" builtinId="19" customBuiltin="1"/>
-    <cellStyle name="Input" xfId="9" builtinId="20" customBuiltin="1"/>
-    <cellStyle name="Linked Cell" xfId="12" builtinId="24" customBuiltin="1"/>
-    <cellStyle name="Neutral" xfId="8" builtinId="28" customBuiltin="1"/>
+    <cellStyle name="Avertissement" xfId="14" builtinId="11" customBuiltin="1"/>
+    <cellStyle name="Calcul" xfId="11" builtinId="22" customBuiltin="1"/>
+    <cellStyle name="Cellule liée" xfId="12" builtinId="24" customBuiltin="1"/>
+    <cellStyle name="Commentaire" xfId="15" builtinId="10" customBuiltin="1"/>
+    <cellStyle name="Entrée" xfId="9" builtinId="20" customBuiltin="1"/>
+    <cellStyle name="Insatisfaisant" xfId="7" builtinId="27" customBuiltin="1"/>
+    <cellStyle name="Neutre" xfId="8" builtinId="28" customBuiltin="1"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Note" xfId="15" builtinId="10" customBuiltin="1"/>
-    <cellStyle name="Output" xfId="10" builtinId="21" customBuiltin="1"/>
-    <cellStyle name="Title" xfId="1" builtinId="15" customBuiltin="1"/>
+    <cellStyle name="Satisfaisant" xfId="6" builtinId="26" customBuiltin="1"/>
+    <cellStyle name="Sortie" xfId="10" builtinId="21" customBuiltin="1"/>
+    <cellStyle name="Texte explicatif" xfId="16" builtinId="53" customBuiltin="1"/>
+    <cellStyle name="Titre" xfId="1" builtinId="15" customBuiltin="1"/>
+    <cellStyle name="Titre 1" xfId="2" builtinId="16" customBuiltin="1"/>
+    <cellStyle name="Titre 2" xfId="3" builtinId="17" customBuiltin="1"/>
+    <cellStyle name="Titre 3" xfId="4" builtinId="18" customBuiltin="1"/>
+    <cellStyle name="Titre 4" xfId="5" builtinId="19" customBuiltin="1"/>
     <cellStyle name="Total" xfId="17" builtinId="25" customBuiltin="1"/>
-    <cellStyle name="Warning Text" xfId="14" builtinId="11" customBuiltin="1"/>
+    <cellStyle name="Vérification" xfId="13" builtinId="23" customBuiltin="1"/>
   </cellStyles>
   <dxfs count="20">
     <dxf>
@@ -1640,7 +1673,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="fr-FR"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -1811,7 +1844,7 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>19</c:v>
+                  <c:v>12</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>0</c:v>
@@ -1820,10 +1853,10 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0</c:v>
+                  <c:v>18</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>60</c:v>
+                  <c:v>49</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2931,7 +2964,7 @@
       </c>
       <c r="G2" s="15"/>
     </row>
-    <row r="3" spans="1:8" ht="33.75">
+    <row r="3" spans="1:8" ht="16.5">
       <c r="A3" s="15" t="s">
         <v>19</v>
       </c>
@@ -2942,22 +2975,22 @@
         <v>21</v>
       </c>
       <c r="D3" s="15" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="E3" s="15" t="s">
-        <v>17</v>
-      </c>
-      <c r="F3" s="17" t="s">
-        <v>22</v>
-      </c>
-      <c r="G3" s="15"/>
+        <v>23</v>
+      </c>
+      <c r="F3" s="17"/>
+      <c r="G3" s="15" t="s">
+        <v>24</v>
+      </c>
     </row>
     <row r="4" spans="1:8" ht="15.95">
       <c r="A4" s="15" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B4" s="15" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C4" s="15" t="s">
         <v>15</v>
@@ -2969,187 +3002,193 @@
         <v>17</v>
       </c>
       <c r="F4" s="15" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="G4" s="15"/>
     </row>
     <row r="5" spans="1:8" ht="15.95">
       <c r="A5" s="15" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B5" s="15" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C5" s="15" t="s">
         <v>15</v>
       </c>
       <c r="D5" s="15" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E5" s="15" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F5" s="15"/>
       <c r="G5" s="15"/>
     </row>
     <row r="6" spans="1:8" ht="15.95">
       <c r="A6" s="15" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B6" s="15" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C6" s="15" t="s">
         <v>21</v>
       </c>
       <c r="D6" s="15" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="E6" s="15" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="F6" s="15"/>
-      <c r="G6" s="15"/>
+      <c r="G6" s="15" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="7" spans="1:8" ht="15.95">
       <c r="A7" s="15" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="B7" s="15" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="C7" s="15" t="s">
         <v>21</v>
       </c>
       <c r="D7" s="15" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="E7" s="15" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="F7" s="15"/>
-      <c r="G7" s="15"/>
+      <c r="G7" s="15" t="s">
+        <v>36</v>
+      </c>
     </row>
     <row r="8" spans="1:8" ht="15.95">
       <c r="A8" s="15" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="B8" s="15" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="C8" s="15" t="s">
         <v>15</v>
       </c>
       <c r="D8" s="15" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="E8" s="15" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="F8" s="15"/>
-      <c r="G8" s="15"/>
+      <c r="G8" s="15" t="s">
+        <v>39</v>
+      </c>
     </row>
     <row r="9" spans="1:8" ht="15.95">
       <c r="A9" s="15" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="B9" s="15" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="C9" s="15" t="s">
         <v>15</v>
       </c>
       <c r="D9" s="15" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E9" s="15" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F9" s="15"/>
       <c r="G9" s="15"/>
     </row>
     <row r="10" spans="1:8" ht="15.95">
       <c r="A10" s="15" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="B10" s="15" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="C10" s="15" t="s">
         <v>15</v>
       </c>
       <c r="D10" s="15" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E10" s="15" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F10" s="15"/>
       <c r="G10" s="15"/>
     </row>
     <row r="11" spans="1:8" ht="17.100000000000001">
       <c r="A11" s="15" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="B11" s="17" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="C11" s="15" t="s">
         <v>21</v>
       </c>
       <c r="D11" s="15" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E11" s="15" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F11" s="15"/>
       <c r="G11" s="15"/>
     </row>
     <row r="12" spans="1:8" ht="15.95">
       <c r="A12" s="15" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="B12" s="15" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="C12" s="15" t="s">
         <v>21</v>
       </c>
       <c r="D12" s="15" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E12" s="15" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F12" s="15"/>
       <c r="G12" s="15"/>
     </row>
     <row r="13" spans="1:8" ht="15.95">
       <c r="A13" s="15" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="B13" s="15" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="C13" s="15" t="s">
         <v>21</v>
       </c>
       <c r="D13" s="15" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E13" s="15" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F13" s="15"/>
       <c r="G13" s="15"/>
     </row>
     <row r="14" spans="1:8" ht="33.75">
       <c r="A14" s="15" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="B14" s="15" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="C14" s="15" t="s">
         <v>15</v>
@@ -3161,16 +3200,16 @@
         <v>17</v>
       </c>
       <c r="F14" s="17" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="G14" s="15"/>
     </row>
     <row r="15" spans="1:8" ht="33.75">
       <c r="A15" s="15" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="B15" s="15" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="C15" s="15" t="s">
         <v>15</v>
@@ -3182,16 +3221,16 @@
         <v>17</v>
       </c>
       <c r="F15" s="17" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="G15" s="15"/>
     </row>
     <row r="16" spans="1:8" ht="33.75">
       <c r="A16" s="15" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="B16" s="15" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="C16" s="15" t="s">
         <v>15</v>
@@ -3203,92 +3242,92 @@
         <v>17</v>
       </c>
       <c r="F16" s="17" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="G16" s="15"/>
     </row>
     <row r="17" spans="1:7" ht="15.95">
       <c r="A17" s="15" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="B17" s="15" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="C17" s="15" t="s">
         <v>15</v>
       </c>
       <c r="D17" s="15" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E17" s="15" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F17" s="15"/>
       <c r="G17" s="15"/>
     </row>
     <row r="18" spans="1:7" ht="15.95">
       <c r="A18" s="15" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="B18" s="15" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C18" s="15" t="s">
         <v>15</v>
       </c>
       <c r="D18" s="15" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E18" s="15" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F18" s="15"/>
       <c r="G18" s="15"/>
     </row>
     <row r="19" spans="1:7" ht="15.95">
       <c r="A19" s="15" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="B19" s="15" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="C19" s="15" t="s">
         <v>21</v>
       </c>
       <c r="D19" s="15" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E19" s="15" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F19" s="15"/>
       <c r="G19" s="15"/>
     </row>
     <row r="20" spans="1:7" ht="15.95">
       <c r="A20" s="15" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="B20" s="15" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="C20" s="15" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="15" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E20" s="15" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F20" s="15"/>
       <c r="G20" s="15"/>
     </row>
     <row r="21" spans="1:7" ht="33.75">
       <c r="A21" s="15" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="B21" s="15" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="C21" s="15" t="s">
         <v>15</v>
@@ -3300,35 +3339,35 @@
         <v>17</v>
       </c>
       <c r="F21" s="17" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="G21" s="15"/>
     </row>
     <row r="22" spans="1:7" ht="15.95">
       <c r="A22" s="15" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="B22" s="15" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="C22" s="15" t="s">
         <v>15</v>
       </c>
       <c r="D22" s="15" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E22" s="15" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F22" s="15"/>
       <c r="G22" s="15"/>
     </row>
     <row r="23" spans="1:7" ht="50.25">
       <c r="A23" s="15" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="B23" s="15" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="C23" s="15" t="s">
         <v>15</v>
@@ -3340,132 +3379,134 @@
         <v>17</v>
       </c>
       <c r="F23" s="17" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="G23" s="15"/>
     </row>
     <row r="24" spans="1:7" ht="15.95">
       <c r="A24" s="15" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="B24" s="15" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="C24" s="15" t="s">
         <v>21</v>
       </c>
       <c r="D24" s="15" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="E24" s="15" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="F24" s="15"/>
-      <c r="G24" s="15"/>
+      <c r="G24" s="15" t="s">
+        <v>77</v>
+      </c>
     </row>
     <row r="25" spans="1:7" ht="15.95">
       <c r="A25" s="15" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="B25" s="15" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="C25" s="15" t="s">
         <v>21</v>
       </c>
       <c r="D25" s="15" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E25" s="15" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F25" s="15"/>
       <c r="G25" s="15"/>
     </row>
     <row r="26" spans="1:7" ht="15.95">
       <c r="A26" s="15" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="B26" s="15" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="C26" s="15" t="s">
         <v>15</v>
       </c>
       <c r="D26" s="15" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E26" s="15" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F26" s="15"/>
       <c r="G26" s="15"/>
     </row>
     <row r="27" spans="1:7" ht="15.95">
       <c r="A27" s="15" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B27" s="15" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="C27" s="15" t="s">
         <v>15</v>
       </c>
       <c r="D27" s="15" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E27" s="15" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F27" s="15"/>
       <c r="G27" s="15"/>
     </row>
-    <row r="28" spans="1:7" ht="33.75">
+    <row r="28" spans="1:7" ht="50.25">
       <c r="A28" s="15" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="B28" s="15" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="C28" s="15" t="s">
         <v>15</v>
       </c>
       <c r="D28" s="15" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="E28" s="15" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="F28" s="17" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="G28" s="15"/>
     </row>
     <row r="29" spans="1:7" ht="15.95">
       <c r="A29" s="15" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="B29" s="15" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="C29" s="15" t="s">
         <v>21</v>
       </c>
       <c r="D29" s="15" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E29" s="15" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F29" s="15"/>
       <c r="G29" s="15"/>
     </row>
     <row r="30" spans="1:7" ht="33.75">
       <c r="A30" s="15" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="B30" s="15" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="C30" s="15" t="s">
         <v>15</v>
@@ -3477,54 +3518,54 @@
         <v>17</v>
       </c>
       <c r="F30" s="17" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="G30" s="15"/>
     </row>
     <row r="31" spans="1:7" ht="15.95">
       <c r="A31" s="15" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="B31" s="15" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="C31" s="15" t="s">
         <v>15</v>
       </c>
       <c r="D31" s="15" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E31" s="15" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F31" s="15"/>
       <c r="G31" s="15"/>
     </row>
     <row r="32" spans="1:7" ht="15.95">
       <c r="A32" s="15" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="B32" s="15" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="C32" s="15" t="s">
         <v>21</v>
       </c>
       <c r="D32" s="15" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E32" s="15" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F32" s="15"/>
       <c r="G32" s="15"/>
     </row>
     <row r="33" spans="1:7" ht="33.75">
       <c r="A33" s="15" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="B33" s="15" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="C33" s="15" t="s">
         <v>15</v>
@@ -3536,73 +3577,73 @@
         <v>17</v>
       </c>
       <c r="F33" s="17" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="G33" s="15"/>
     </row>
     <row r="34" spans="1:7" ht="15.95">
       <c r="A34" s="15" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="B34" s="15" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="C34" s="15" t="s">
         <v>15</v>
       </c>
       <c r="D34" s="15" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E34" s="15" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F34" s="15"/>
       <c r="G34" s="15"/>
     </row>
     <row r="35" spans="1:7" ht="15.95">
       <c r="A35" s="15" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="B35" s="15" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="C35" s="15" t="s">
         <v>21</v>
       </c>
       <c r="D35" s="15" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E35" s="15" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F35" s="15"/>
       <c r="G35" s="15"/>
     </row>
     <row r="36" spans="1:7" ht="15.95">
       <c r="A36" s="15" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="B36" s="15" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="C36" s="15" t="s">
         <v>21</v>
       </c>
       <c r="D36" s="15" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E36" s="15" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F36" s="15"/>
       <c r="G36" s="15"/>
     </row>
     <row r="37" spans="1:7" ht="33.75">
       <c r="A37" s="15" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="B37" s="15" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="C37" s="15" t="s">
         <v>15</v>
@@ -3614,153 +3655,153 @@
         <v>17</v>
       </c>
       <c r="F37" s="17" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="G37" s="15"/>
     </row>
-    <row r="38" spans="1:7" ht="50.25">
+    <row r="38" spans="1:7" ht="16.5">
       <c r="A38" s="15" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="B38" s="15" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="C38" s="15" t="s">
         <v>15</v>
       </c>
       <c r="D38" s="15" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="E38" s="15" t="s">
-        <v>17</v>
-      </c>
-      <c r="F38" s="17" t="s">
-        <v>104</v>
-      </c>
-      <c r="G38" s="15"/>
+        <v>23</v>
+      </c>
+      <c r="F38" s="17"/>
+      <c r="G38" s="15" t="s">
+        <v>110</v>
+      </c>
     </row>
     <row r="39" spans="1:7" ht="15.95">
       <c r="A39" s="15" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="B39" s="15" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="C39" s="15" t="s">
         <v>15</v>
       </c>
       <c r="D39" s="15" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E39" s="15" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F39" s="15"/>
       <c r="G39" s="15"/>
     </row>
     <row r="40" spans="1:7" ht="15.95">
       <c r="A40" s="15" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="B40" s="15" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="C40" s="15" t="s">
         <v>15</v>
       </c>
       <c r="D40" s="15" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E40" s="15" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F40" s="15"/>
       <c r="G40" s="15"/>
     </row>
     <row r="41" spans="1:7" ht="15.95">
       <c r="A41" s="15" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="B41" s="15" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="C41" s="15" t="s">
         <v>21</v>
       </c>
       <c r="D41" s="15" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E41" s="15" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F41" s="15"/>
       <c r="G41" s="15"/>
     </row>
-    <row r="42" spans="1:7" ht="33.75">
+    <row r="42" spans="1:7" ht="16.5">
       <c r="A42" s="15" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="B42" s="15" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="C42" s="15" t="s">
         <v>21</v>
       </c>
       <c r="D42" s="15" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="E42" s="15" t="s">
-        <v>17</v>
-      </c>
-      <c r="F42" s="17" t="s">
-        <v>113</v>
-      </c>
-      <c r="G42" s="15"/>
+        <v>23</v>
+      </c>
+      <c r="F42" s="17"/>
+      <c r="G42" s="15" t="s">
+        <v>119</v>
+      </c>
     </row>
     <row r="43" spans="1:7" ht="15.95">
       <c r="A43" s="15" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="B43" s="15" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="C43" s="15" t="s">
         <v>21</v>
       </c>
       <c r="D43" s="15" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E43" s="15" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F43" s="15"/>
       <c r="G43" s="15"/>
     </row>
     <row r="44" spans="1:7" ht="15.95">
       <c r="A44" s="15" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="B44" s="15" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="C44" s="15" t="s">
         <v>15</v>
       </c>
       <c r="D44" s="15" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E44" s="15" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F44" s="15"/>
       <c r="G44" s="15"/>
     </row>
     <row r="45" spans="1:7" ht="33.75">
       <c r="A45" s="15" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="B45" s="15" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="C45" s="15" t="s">
         <v>15</v>
@@ -3772,113 +3813,113 @@
         <v>17</v>
       </c>
       <c r="F45" s="17" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="G45" s="15"/>
     </row>
     <row r="46" spans="1:7" ht="15.95">
       <c r="A46" s="15" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="B46" s="15" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="C46" s="15" t="s">
         <v>15</v>
       </c>
       <c r="D46" s="15" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E46" s="15" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F46" s="15"/>
       <c r="G46" s="15"/>
     </row>
-    <row r="47" spans="1:7" ht="50.25">
+    <row r="47" spans="1:7" ht="16.5">
       <c r="A47" s="15" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="B47" s="15" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="C47" s="15" t="s">
         <v>15</v>
       </c>
       <c r="D47" s="15" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="E47" s="15" t="s">
-        <v>17</v>
-      </c>
-      <c r="F47" s="17" t="s">
-        <v>125</v>
-      </c>
-      <c r="G47" s="15"/>
+        <v>23</v>
+      </c>
+      <c r="F47" s="17"/>
+      <c r="G47" s="15" t="s">
+        <v>131</v>
+      </c>
     </row>
     <row r="48" spans="1:7" ht="15.95">
       <c r="A48" s="15" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="B48" s="15" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="C48" s="15" t="s">
         <v>15</v>
       </c>
       <c r="D48" s="15" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E48" s="15" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F48" s="15"/>
       <c r="G48" s="15"/>
     </row>
     <row r="49" spans="1:7" ht="15.95">
       <c r="A49" s="15" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="B49" s="15" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="C49" s="15" t="s">
         <v>15</v>
       </c>
       <c r="D49" s="15" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E49" s="15" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F49" s="15"/>
       <c r="G49" s="15"/>
     </row>
     <row r="50" spans="1:7" ht="15.95">
       <c r="A50" s="15" t="s">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="B50" s="15" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="C50" s="15" t="s">
         <v>15</v>
       </c>
       <c r="D50" s="15" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E50" s="15" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F50" s="15"/>
       <c r="G50" s="15"/>
     </row>
     <row r="51" spans="1:7" ht="33.75">
       <c r="A51" s="15" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="B51" s="15" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="C51" s="15" t="s">
         <v>15</v>
@@ -3890,561 +3931,575 @@
         <v>17</v>
       </c>
       <c r="F51" s="17" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="G51" s="15"/>
     </row>
     <row r="52" spans="1:7" ht="15.95">
       <c r="A52" s="15" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="B52" s="15" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="C52" s="15" t="s">
         <v>15</v>
       </c>
       <c r="D52" s="15" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E52" s="15" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F52" s="15"/>
       <c r="G52" s="15"/>
     </row>
     <row r="53" spans="1:7" ht="15.95">
       <c r="A53" s="15" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="B53" s="15" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="C53" s="15" t="s">
         <v>21</v>
       </c>
       <c r="D53" s="15" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E53" s="15" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F53" s="15"/>
       <c r="G53" s="15"/>
     </row>
     <row r="54" spans="1:7" ht="15.95">
       <c r="A54" s="15" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="B54" s="15" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="C54" s="15" t="s">
         <v>21</v>
       </c>
       <c r="D54" s="15" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E54" s="15" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F54" s="15"/>
       <c r="G54" s="15"/>
     </row>
     <row r="55" spans="1:7" ht="15.95">
       <c r="A55" s="15" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="B55" s="15" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="C55" s="15" t="s">
         <v>21</v>
       </c>
       <c r="D55" s="15" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E55" s="15" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F55" s="15"/>
       <c r="G55" s="15"/>
     </row>
-    <row r="56" spans="1:7" ht="33.75">
+    <row r="56" spans="1:7" ht="16.5">
       <c r="A56" s="15" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="B56" s="15" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="C56" s="15" t="s">
         <v>21</v>
       </c>
       <c r="D56" s="15" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="E56" s="15" t="s">
-        <v>17</v>
-      </c>
-      <c r="F56" s="17" t="s">
-        <v>145</v>
-      </c>
-      <c r="G56" s="15"/>
+        <v>23</v>
+      </c>
+      <c r="F56" s="17"/>
+      <c r="G56" s="15" t="s">
+        <v>151</v>
+      </c>
     </row>
     <row r="57" spans="1:7" ht="15.95">
       <c r="A57" s="15" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="B57" s="15" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="C57" s="15" t="s">
         <v>21</v>
       </c>
       <c r="D57" s="15" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E57" s="15" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F57" s="15"/>
       <c r="G57" s="15"/>
     </row>
     <row r="58" spans="1:7" ht="15.95">
       <c r="A58" s="15" t="s">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="B58" s="15" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="C58" s="15" t="s">
         <v>15</v>
       </c>
       <c r="D58" s="15" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E58" s="15" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F58" s="15"/>
       <c r="G58" s="15"/>
     </row>
     <row r="59" spans="1:7" ht="15.95">
       <c r="A59" s="15" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="B59" s="15" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="C59" s="15" t="s">
         <v>15</v>
       </c>
       <c r="D59" s="15" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E59" s="15" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F59" s="15"/>
       <c r="G59" s="15"/>
     </row>
     <row r="60" spans="1:7" ht="15.95">
       <c r="A60" s="15" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="B60" s="15" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="C60" s="15" t="s">
         <v>15</v>
       </c>
       <c r="D60" s="15" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E60" s="15" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F60" s="15"/>
       <c r="G60" s="15"/>
     </row>
     <row r="61" spans="1:7" ht="15.95">
       <c r="A61" s="15" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="B61" s="15" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="C61" s="15" t="s">
         <v>15</v>
       </c>
       <c r="D61" s="15" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="E61" s="15" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F61" s="15"/>
       <c r="G61" s="15"/>
     </row>
     <row r="62" spans="1:7" ht="15.95">
       <c r="A62" s="15" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="B62" s="15" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="C62" s="15" t="s">
         <v>15</v>
       </c>
       <c r="D62" s="15" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E62" s="15" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F62" s="15"/>
       <c r="G62" s="15"/>
     </row>
     <row r="63" spans="1:7" ht="15.95">
       <c r="A63" s="15" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="B63" s="15" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="C63" s="15" t="s">
         <v>15</v>
       </c>
       <c r="D63" s="15" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E63" s="15" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F63" s="15"/>
       <c r="G63" s="15"/>
     </row>
     <row r="64" spans="1:7" ht="15.95">
       <c r="A64" s="15" t="s">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="B64" s="15" t="s">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="C64" s="15" t="s">
         <v>15</v>
       </c>
       <c r="D64" s="15" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E64" s="15" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F64" s="15"/>
       <c r="G64" s="15"/>
     </row>
-    <row r="65" spans="1:7" ht="50.25">
+    <row r="65" spans="1:7" ht="16.5">
       <c r="A65" s="15" t="s">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="B65" s="15" t="s">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="C65" s="15" t="s">
         <v>15</v>
       </c>
       <c r="D65" s="15" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="E65" s="15" t="s">
-        <v>17</v>
-      </c>
-      <c r="F65" s="17" t="s">
-        <v>164</v>
-      </c>
-      <c r="G65" s="15"/>
+        <v>23</v>
+      </c>
+      <c r="F65" s="17"/>
+      <c r="G65" s="15" t="s">
+        <v>170</v>
+      </c>
     </row>
     <row r="66" spans="1:7" ht="15.95">
       <c r="A66" s="15" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="B66" s="15" t="s">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="C66" s="15" t="s">
         <v>21</v>
       </c>
       <c r="D66" s="15" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="E66" s="15" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="F66" s="15"/>
-      <c r="G66" s="15"/>
+      <c r="G66" s="15" t="s">
+        <v>173</v>
+      </c>
     </row>
     <row r="67" spans="1:7" ht="15.95">
       <c r="A67" s="15" t="s">
-        <v>167</v>
+        <v>174</v>
       </c>
       <c r="B67" s="15" t="s">
-        <v>168</v>
+        <v>175</v>
       </c>
       <c r="C67" s="15" t="s">
         <v>15</v>
       </c>
       <c r="D67" s="15" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E67" s="15" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F67" s="15"/>
       <c r="G67" s="15"/>
     </row>
     <row r="68" spans="1:7" ht="15.95">
       <c r="A68" s="15" t="s">
-        <v>169</v>
+        <v>176</v>
       </c>
       <c r="B68" s="15" t="s">
-        <v>170</v>
+        <v>177</v>
       </c>
       <c r="C68" s="15" t="s">
         <v>15</v>
       </c>
       <c r="D68" s="15" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E68" s="15" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F68" s="15"/>
       <c r="G68" s="15"/>
     </row>
     <row r="69" spans="1:7" ht="15.95">
       <c r="A69" s="15" t="s">
-        <v>171</v>
+        <v>178</v>
       </c>
       <c r="B69" s="15" t="s">
-        <v>172</v>
+        <v>179</v>
       </c>
       <c r="C69" s="15" t="s">
         <v>15</v>
       </c>
       <c r="D69" s="15" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E69" s="15" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F69" s="15"/>
       <c r="G69" s="15"/>
     </row>
     <row r="70" spans="1:7" ht="15.95">
       <c r="A70" s="15" t="s">
-        <v>173</v>
+        <v>180</v>
       </c>
       <c r="B70" s="15" t="s">
-        <v>174</v>
+        <v>181</v>
       </c>
       <c r="C70" s="15" t="s">
         <v>21</v>
       </c>
       <c r="D70" s="15" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E70" s="15" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F70" s="15"/>
       <c r="G70" s="15"/>
     </row>
     <row r="71" spans="1:7" ht="15.95">
       <c r="A71" s="15" t="s">
-        <v>175</v>
+        <v>182</v>
       </c>
       <c r="B71" s="15" t="s">
-        <v>176</v>
+        <v>183</v>
       </c>
       <c r="C71" s="15" t="s">
         <v>15</v>
       </c>
       <c r="D71" s="15" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E71" s="15" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F71" s="15"/>
       <c r="G71" s="15"/>
     </row>
     <row r="72" spans="1:7" ht="15.95">
       <c r="A72" s="15" t="s">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="B72" s="15" t="s">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="C72" s="15" t="s">
         <v>15</v>
       </c>
       <c r="D72" s="15" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E72" s="15" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F72" s="15"/>
       <c r="G72" s="15"/>
     </row>
     <row r="73" spans="1:7" ht="15.95">
       <c r="A73" s="15" t="s">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="B73" s="15" t="s">
-        <v>180</v>
+        <v>187</v>
       </c>
       <c r="C73" s="15" t="s">
         <v>15</v>
       </c>
       <c r="D73" s="15" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="E73" s="15" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="F73" s="15"/>
-      <c r="G73" s="15"/>
+      <c r="G73" s="15" t="s">
+        <v>188</v>
+      </c>
     </row>
     <row r="74" spans="1:7" ht="15.95">
       <c r="A74" s="15" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="B74" s="15" t="s">
-        <v>182</v>
+        <v>190</v>
       </c>
       <c r="C74" s="15" t="s">
         <v>15</v>
       </c>
       <c r="D74" s="15" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E74" s="15" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F74" s="15"/>
       <c r="G74" s="15"/>
     </row>
     <row r="75" spans="1:7" ht="15.95">
       <c r="A75" s="15" t="s">
-        <v>183</v>
+        <v>191</v>
       </c>
       <c r="B75" s="15" t="s">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="C75" s="15" t="s">
         <v>15</v>
       </c>
       <c r="D75" s="15" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="E75" s="15" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="F75" s="15"/>
-      <c r="G75" s="15"/>
+      <c r="G75" s="15" t="s">
+        <v>193</v>
+      </c>
     </row>
     <row r="76" spans="1:7" ht="15.95">
       <c r="A76" s="15" t="s">
-        <v>185</v>
+        <v>194</v>
       </c>
       <c r="B76" s="15" t="s">
-        <v>186</v>
+        <v>195</v>
       </c>
       <c r="C76" s="15" t="s">
         <v>15</v>
       </c>
       <c r="D76" s="15" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="E76" s="15" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="F76" s="15"/>
-      <c r="G76" s="15"/>
+      <c r="G76" s="15" t="s">
+        <v>196</v>
+      </c>
     </row>
     <row r="77" spans="1:7" ht="15.95">
       <c r="A77" s="15" t="s">
-        <v>187</v>
+        <v>197</v>
       </c>
       <c r="B77" s="15" t="s">
-        <v>188</v>
+        <v>198</v>
       </c>
       <c r="C77" s="15" t="s">
         <v>21</v>
       </c>
       <c r="D77" s="15" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="E77" s="15" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="F77" s="15"/>
-      <c r="G77" s="15"/>
+      <c r="G77" s="15" t="s">
+        <v>199</v>
+      </c>
     </row>
     <row r="78" spans="1:7" ht="15.95">
       <c r="A78" s="15" t="s">
-        <v>189</v>
+        <v>200</v>
       </c>
       <c r="B78" s="15" t="s">
-        <v>190</v>
+        <v>201</v>
       </c>
       <c r="C78" s="15" t="s">
         <v>15</v>
       </c>
       <c r="D78" s="15" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="E78" s="15" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="F78" s="15"/>
-      <c r="G78" s="15"/>
+      <c r="G78" s="15" t="s">
+        <v>202</v>
+      </c>
     </row>
     <row r="79" spans="1:7" ht="15.95">
       <c r="A79" s="15" t="s">
-        <v>191</v>
+        <v>203</v>
       </c>
       <c r="B79" s="15" t="s">
-        <v>192</v>
+        <v>204</v>
       </c>
       <c r="C79" s="15" t="s">
         <v>15</v>
       </c>
       <c r="D79" s="15" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="E79" s="15" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="F79" s="15"/>
-      <c r="G79" s="15"/>
+      <c r="G79" s="15" t="s">
+        <v>205</v>
+      </c>
     </row>
     <row r="80" spans="1:7" ht="15.95">
       <c r="A80" s="15" t="s">
-        <v>193</v>
+        <v>206</v>
       </c>
       <c r="B80" s="15" t="s">
-        <v>194</v>
+        <v>207</v>
       </c>
       <c r="C80" s="15" t="s">
         <v>15</v>
       </c>
       <c r="D80" s="15" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E80" s="15" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F80" s="15"/>
       <c r="G80" s="15"/>
@@ -4539,15 +4594,15 @@
   <sheetData>
     <row r="23" spans="2:3">
       <c r="B23" s="1" t="s">
-        <v>195</v>
+        <v>208</v>
       </c>
     </row>
     <row r="25" spans="2:3">
       <c r="B25" s="11" t="s">
-        <v>196</v>
+        <v>209</v>
       </c>
       <c r="C25" s="11" t="s">
-        <v>197</v>
+        <v>210</v>
       </c>
     </row>
     <row r="26" spans="2:3">
@@ -4556,12 +4611,12 @@
       </c>
       <c r="C26" s="11">
         <f>COUNTIF('Recommandations guide ANSSI'!E:E,B26)</f>
-        <v>19</v>
+        <v>12</v>
       </c>
     </row>
     <row r="27" spans="2:3">
       <c r="B27" s="11" t="s">
-        <v>198</v>
+        <v>211</v>
       </c>
       <c r="C27" s="11">
         <f>COUNTIF('Recommandations guide ANSSI'!E:E,B27)</f>
@@ -4570,7 +4625,7 @@
     </row>
     <row r="28" spans="2:3">
       <c r="B28" s="11" t="s">
-        <v>199</v>
+        <v>212</v>
       </c>
       <c r="C28" s="11">
         <f>COUNTIF('Recommandations guide ANSSI'!E:E,B28)</f>
@@ -4579,20 +4634,20 @@
     </row>
     <row r="29" spans="2:3">
       <c r="B29" s="11" t="s">
-        <v>200</v>
+        <v>23</v>
       </c>
       <c r="C29" s="11">
         <f>COUNTIF('Recommandations guide ANSSI'!E:E,B29)</f>
-        <v>0</v>
+        <v>18</v>
       </c>
     </row>
     <row r="30" spans="2:3">
       <c r="B30" s="11" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C30" s="11">
         <f>COUNTIF('Recommandations guide ANSSI'!E:E,B30)</f>
-        <v>60</v>
+        <v>49</v>
       </c>
     </row>
   </sheetData>
@@ -4623,12 +4678,12 @@
   <sheetData>
     <row r="2" spans="2:4">
       <c r="B2" s="1" t="s">
-        <v>201</v>
+        <v>213</v>
       </c>
     </row>
     <row r="3" spans="2:4">
       <c r="B3" s="9" t="s">
-        <v>202</v>
+        <v>214</v>
       </c>
     </row>
     <row r="5" spans="2:4" ht="30">
@@ -4650,28 +4705,28 @@
     </row>
     <row r="7" spans="2:4">
       <c r="B7" s="12" t="s">
-        <v>203</v>
+        <v>22</v>
       </c>
       <c r="D7" s="12" t="s">
-        <v>198</v>
+        <v>211</v>
       </c>
     </row>
     <row r="8" spans="2:4">
       <c r="B8" s="12" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>199</v>
+        <v>212</v>
       </c>
     </row>
     <row r="9" spans="2:4">
       <c r="D9" s="12" t="s">
-        <v>200</v>
+        <v>23</v>
       </c>
     </row>
     <row r="10" spans="2:4">
       <c r="D10" s="12" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
   </sheetData>
